--- a/Avaliações dos Itens/Avaliações (2008-2024)/2024 nível junior.xlsx
+++ b/Avaliações dos Itens/Avaliações (2008-2024)/2024 nível junior.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/criterios por questoes e provas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{A06599FD-C66A-4A14-B628-69F956B5E6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08BD6EA-2C0E-4148-8BDD-1C3C8A3B126E}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{A06599FD-C66A-4A14-B628-69F956B5E6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A783199-DA37-4A76-BA87-E2C9960EF718}"/>
   <bookViews>
     <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" xr2:uid="{069F386B-0675-4193-84C5-D5BC18E0BF61}"/>
   </bookViews>
@@ -151,10 +146,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -659,5 +650,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>